--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Europe UEFA Champions League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Europe UEFA Champions League_20242025.xlsx
@@ -1042,7 +1042,7 @@
     <t>['62']</t>
   </si>
   <si>
-    <t>['90+2', '102']</t>
+    <t>['102', '90+2']</t>
   </si>
   <si>
     <t>['45']</t>
@@ -1129,7 +1129,7 @@
     <t>['10', '45', '90+6', '99']</t>
   </si>
   <si>
-    <t>['7', '45+1', '45+5', '93', '110', '112', '118']</t>
+    <t>['7', '110', '112', '118', '45+1', '45+5', '93']</t>
   </si>
   <si>
     <t>['50']</t>
